--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -658,11 +658,9 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3574507960520268</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="b">
         <v>1</v>
       </c>
@@ -692,29 +690,27 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0.9067348049549744</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -724,7 +720,7 @@
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB2" t="n">
         <v>1.221670955679069</v>
@@ -733,7 +729,7 @@
         <v>4.970152414187585</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.8577895692908324</v>
+        <v>1.643051814352494</v>
       </c>
     </row>
     <row r="3">
@@ -745,12 +741,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -760,11 +756,9 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.3696520502165128</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="b">
         <v>1</v>
       </c>
@@ -794,29 +788,27 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>1.682681605370389</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -826,7 +818,7 @@
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB3" t="n">
         <v>1.220338486610837</v>
@@ -835,7 +827,7 @@
         <v>4.968442038578913</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5794955944265724</v>
+        <v>0.2173776722779184</v>
       </c>
     </row>
     <row r="4">
@@ -847,12 +839,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -862,11 +854,9 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.3813898345828795</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="b">
         <v>1</v>
       </c>
@@ -896,29 +886,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>1.635072055436547</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -928,7 +916,7 @@
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB4" t="n">
         <v>1.220338486610837</v>
@@ -937,7 +925,7 @@
         <v>4.648671535445624</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.650936713524944</v>
+        <v>0.7946744136122106</v>
       </c>
     </row>
     <row r="5">
@@ -949,12 +937,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -964,11 +952,9 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3873649072076715</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="b">
         <v>1</v>
       </c>
@@ -998,29 +984,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>1.313331509285081</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1030,7 +1014,7 @@
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB5" t="n">
         <v>1.220338486610837</v>
@@ -1039,7 +1023,7 @@
         <v>4.87389129925047</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.460352580634151</v>
+        <v>0.6502118169503136</v>
       </c>
     </row>
     <row r="6">
@@ -1051,12 +1035,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1066,11 +1050,9 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.4009811485705428</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="b">
         <v>1</v>
       </c>
@@ -1100,29 +1082,27 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>1.703018838801081</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1132,7 +1112,7 @@
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB6" t="n">
         <v>1.220338486610837</v>
@@ -1141,7 +1121,7 @@
         <v>4.805706648106417</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.078881165886732</v>
+        <v>1.22274805256236</v>
       </c>
     </row>
     <row r="7">
@@ -1153,12 +1133,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1168,11 +1148,9 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.4019162772377667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="b">
         <v>1</v>
       </c>
@@ -1202,29 +1180,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>1.046642026467208</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1234,7 +1210,7 @@
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB7" t="n">
         <v>1.220338486610837</v>
@@ -1243,7 +1219,7 @@
         <v>4.854407394698442</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32895899204134</v>
+        <v>0.478413146292047</v>
       </c>
     </row>
     <row r="8">
@@ -1255,12 +1231,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1270,11 +1246,9 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3922097690925458</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="b">
         <v>1</v>
       </c>
@@ -1304,29 +1278,27 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>0.5169885523457552</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1336,7 +1308,7 @@
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB8" t="n">
         <v>1.220338486610837</v>
@@ -1345,7 +1317,7 @@
         <v>4.852418761303465</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.6172074280171629</v>
+        <v>0.2206628196833151</v>
       </c>
     </row>
     <row r="9">
@@ -1357,12 +1329,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1372,11 +1344,9 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.3776356828254333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="b">
         <v>1</v>
       </c>
@@ -1406,29 +1376,27 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>0.2568218634210733</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1438,7 +1406,7 @@
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB9" t="n">
         <v>1.220674594082206</v>
@@ -1447,7 +1415,7 @@
         <v>4.406038751020796</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.4118575652313685</v>
+        <v>0.5923733390842153</v>
       </c>
     </row>
     <row r="10">
@@ -1459,12 +1427,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1474,11 +1442,9 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3598559061549448</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="b">
         <v>1</v>
       </c>
@@ -1508,29 +1474,27 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>0.05836352447088801</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1540,7 +1504,7 @@
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB10" t="n">
         <v>1.220674594082206</v>
@@ -1549,7 +1513,7 @@
         <v>4.345464896032414</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2360271014561047</v>
+        <v>1.194961228582783</v>
       </c>
     </row>
     <row r="11">
@@ -1561,12 +1525,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1576,11 +1540,9 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.3598559061549448</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="b">
         <v>1</v>
       </c>
@@ -1610,29 +1572,27 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>soft_fail</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>soft_quality_gate</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>0.1139368099399546</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1642,7 +1602,7 @@
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB11" t="n">
         <v>1.220674594082206</v>
@@ -1651,7 +1611,7 @@
         <v>4.423610029554998</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0431242280054984</v>
+        <v>0.7548383295207802</v>
       </c>
     </row>
     <row r="12">
@@ -1663,12 +1623,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1678,11 +1638,9 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.3561821921171023</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="b">
         <v>1</v>
       </c>
@@ -1712,29 +1670,27 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>0.7958230516710969</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1744,7 +1700,7 @@
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
-        <v>4.074099133996071</v>
+        <v>3.75989792451045</v>
       </c>
       <c r="AB12" t="n">
         <v>1.220674594082206</v>
@@ -1753,7 +1709,7 @@
         <v>4.649945318792187</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.8331678232412325</v>
+        <v>0.09204862177706988</v>
       </c>
     </row>
     <row r="13">
@@ -1765,12 +1721,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SustainedAnomaly</t>
+          <t>BaselinePending</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1780,11 +1736,9 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3697426376541033</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="b">
         <v>1</v>
       </c>
@@ -1792,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1814,29 +1768,27 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>sustained_local_baseline_active</t>
+          <t>baseline_pending_causal_accumulation</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>all_recovery_gates</t>
+          <t>local_baseline_unavailable</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>contextual</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>1.761433100088439</v>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1846,7 +1798,7 @@
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
-        <v>4.222746217519008</v>
+        <v>4.97900378220456</v>
       </c>
       <c r="AB13" t="n">
         <v>1.220674594082206</v>
@@ -1855,7 +1807,7 @@
         <v>4.591910577486482</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.618093928750518</v>
+        <v>0.8780708667418948</v>
       </c>
     </row>
     <row r="14">
@@ -1886,7 +1838,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="b">
@@ -1948,7 +1900,7 @@
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
-        <v>4.35255514740332</v>
+        <v>3.75989792451045</v>
       </c>
       <c r="AB14" t="n">
         <v>1.220674594082206</v>
@@ -1957,7 +1909,7 @@
         <v>4.402543476791452</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.117291843311198</v>
+        <v>1.447306261150455</v>
       </c>
     </row>
     <row r="15">
@@ -1988,7 +1940,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="b">
@@ -2050,7 +2002,7 @@
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB15" t="n">
         <v>1.184556053718251</v>
@@ -2059,7 +2011,7 @@
         <v>4.382194307809452</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.817568971046704</v>
+        <v>1.079450638217308</v>
       </c>
     </row>
     <row r="16">
@@ -2090,7 +2042,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="b">
@@ -2152,7 +2104,7 @@
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB16" t="n">
         <v>1.184556053718251</v>
@@ -2161,7 +2113,7 @@
         <v>4.394069104186509</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.9852475265210102</v>
+        <v>0.07314483502414493</v>
       </c>
     </row>
     <row r="17">
@@ -2192,7 +2144,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="b">
@@ -2254,7 +2206,7 @@
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB17" t="n">
         <v>1.184556053718251</v>
@@ -2263,7 +2215,7 @@
         <v>4.314918517190196</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.7292617867489474</v>
+        <v>0.3329388452569901</v>
       </c>
     </row>
     <row r="18">
@@ -2294,7 +2246,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="b">
@@ -2356,7 +2308,7 @@
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB18" t="n">
         <v>1.184556053718251</v>
@@ -2365,7 +2317,7 @@
         <v>4.424976782980464</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.2266376682107539</v>
+        <v>0.7726955405047002</v>
       </c>
     </row>
     <row r="19">
@@ -2396,7 +2348,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="b">
@@ -2458,7 +2410,7 @@
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB19" t="n">
         <v>1.184556053718251</v>
@@ -2467,7 +2419,7 @@
         <v>4.465592135591619</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2863525109504081</v>
+        <v>1.211689622831859</v>
       </c>
     </row>
     <row r="20">
@@ -2498,7 +2450,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="b">
@@ -2560,7 +2512,7 @@
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB20" t="n">
         <v>1.184556053718251</v>
@@ -2569,7 +2521,7 @@
         <v>4.768695298812885</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.06486485980131</v>
+        <v>2.045618619858192</v>
       </c>
     </row>
     <row r="21">
@@ -2600,7 +2552,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="b">
@@ -2662,7 +2614,7 @@
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB21" t="n">
         <v>1.27814327133518</v>
@@ -2671,7 +2623,7 @@
         <v>4.911356191378412</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.6718335080078797</v>
+        <v>1.43710851581821</v>
       </c>
     </row>
     <row r="22">
@@ -2702,7 +2654,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="b">
@@ -2764,7 +2716,7 @@
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB22" t="n">
         <v>1.27814327133518</v>
@@ -2773,7 +2725,7 @@
         <v>4.917200999172779</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.268223184977517</v>
+        <v>0.788007983380616</v>
       </c>
     </row>
     <row r="23">
@@ -2804,7 +2756,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="b">
@@ -2866,7 +2818,7 @@
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB23" t="n">
         <v>1.27814327133518</v>
@@ -2875,7 +2827,7 @@
         <v>4.928901309750328</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.464023546623538</v>
+        <v>1.080950929866718</v>
       </c>
     </row>
     <row r="24">
@@ -2906,7 +2858,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="b">
@@ -2968,7 +2920,7 @@
       </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB24" t="n">
         <v>1.27814327133518</v>
@@ -2977,7 +2929,7 @@
         <v>4.944067367291508</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.412451056359412</v>
+        <v>1.175617692263491</v>
       </c>
     </row>
     <row r="25">
@@ -3008,7 +2960,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="b">
@@ -3070,7 +3022,7 @@
       </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB25" t="n">
         <v>1.27814327133518</v>
@@ -3079,7 +3031,7 @@
         <v>4.995120572504947</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.289004131849454</v>
+        <v>1.046158279549101</v>
       </c>
     </row>
     <row r="26">
@@ -3110,7 +3062,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="b">
@@ -3172,7 +3124,7 @@
       </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB26" t="n">
         <v>1.27814327133518</v>
@@ -3181,7 +3133,7 @@
         <v>4.99839101612152</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5168740240873542</v>
+        <v>0.9576316082836654</v>
       </c>
     </row>
     <row r="27">
@@ -3212,7 +3164,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="b">
@@ -3274,7 +3226,7 @@
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB27" t="n">
         <v>1.262057531102819</v>
@@ -3283,7 +3235,7 @@
         <v>4.989273988747644</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.5699848327284972</v>
+        <v>0.04162288426127603</v>
       </c>
     </row>
     <row r="28">
@@ -3314,7 +3266,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="b">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
-        <v>4.600998043521259</v>
+        <v>4.995549855868559</v>
       </c>
       <c r="AB28" t="n">
         <v>1.262057531102819</v>
@@ -3385,7 +3337,7 @@
         <v>4.814646576818159</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.230540380992083</v>
+        <v>1.752908310555113</v>
       </c>
     </row>
     <row r="29">
@@ -3416,7 +3368,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="b">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
-        <v>4.600998043521259</v>
+        <v>4.995549855868559</v>
       </c>
       <c r="AB29" t="n">
         <v>1.262057531102819</v>
@@ -3487,7 +3439,7 @@
         <v>4.495022869663774</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.807168069676615</v>
+        <v>2.258985317432974</v>
       </c>
     </row>
     <row r="30">
@@ -3518,7 +3470,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="b">
@@ -3580,7 +3532,7 @@
       </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB30" t="n">
         <v>1.262057531102819</v>
@@ -3589,7 +3541,7 @@
         <v>4.524212148194966</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.97047451771696</v>
+        <v>3.588729707116176</v>
       </c>
     </row>
     <row r="31">
@@ -3620,7 +3572,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="b">
@@ -3682,7 +3634,7 @@
       </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB31" t="n">
         <v>1.262057531102819</v>
@@ -3691,7 +3643,7 @@
         <v>4.356601333163463</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.279955485830806</v>
+        <v>2.723566614543039</v>
       </c>
     </row>
     <row r="32">
@@ -3722,7 +3674,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="b">
@@ -3784,7 +3736,7 @@
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB32" t="n">
         <v>1.262057531102819</v>
@@ -3793,7 +3745,7 @@
         <v>4.294503576556583</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.342632575786631</v>
+        <v>0.7657896930944723</v>
       </c>
     </row>
     <row r="33">
@@ -3824,7 +3776,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="b">
@@ -3886,7 +3838,7 @@
       </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB33" t="n">
         <v>1.2489607973639</v>
@@ -3895,7 +3847,7 @@
         <v>4.602210555719383</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.2492552058631156</v>
+        <v>1.183149970580462</v>
       </c>
     </row>
     <row r="34">
@@ -3926,7 +3878,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="b">
@@ -3988,7 +3940,7 @@
       </c>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB34" t="n">
         <v>1.2489607973639</v>
@@ -3997,7 +3949,7 @@
         <v>4.511791149799965</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.126942028946338</v>
+        <v>1.859570103809255</v>
       </c>
     </row>
     <row r="35">
@@ -4028,7 +3980,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="b">
@@ -4090,7 +4042,7 @@
       </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB35" t="n">
         <v>1.2489607973639</v>
@@ -4099,7 +4051,7 @@
         <v>4.364824994424494</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.8902923420364769</v>
+        <v>1.532595391411145</v>
       </c>
     </row>
     <row r="36">
@@ -4130,7 +4082,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="b">
@@ -4192,7 +4144,7 @@
       </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB36" t="n">
         <v>1.2489607973639</v>
@@ -4201,7 +4153,7 @@
         <v>4.376157691530376</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.01447949776022131</v>
+        <v>0.4489234406318738</v>
       </c>
     </row>
     <row r="37">
@@ -4232,7 +4184,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="b">
@@ -4294,7 +4246,7 @@
       </c>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="n">
-        <v>2.541622006929802</v>
+        <v>4.250200828017036</v>
       </c>
       <c r="AB37" t="n">
         <v>1.2489607973639</v>
@@ -4303,7 +4255,7 @@
         <v>4.433234664269991</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.430783102988436</v>
+        <v>0.8928172914714236</v>
       </c>
     </row>
     <row r="38">
@@ -4334,7 +4286,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="b">
@@ -4396,7 +4348,7 @@
       </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
-        <v>2.866863846995475</v>
+        <v>4.576404151056328</v>
       </c>
       <c r="AB38" t="n">
         <v>1.2489607973639</v>
@@ -4405,7 +4357,7 @@
         <v>4.401588650816791</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.507927823420566</v>
+        <v>1.157889205427296</v>
       </c>
     </row>
     <row r="39">
@@ -4436,7 +4388,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="b">
@@ -4498,7 +4450,7 @@
       </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB39" t="n">
         <v>1.234112340940881</v>
@@ -4507,7 +4459,7 @@
         <v>4.362202922749047</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.6821889050102778</v>
+        <v>0.1415428793617649</v>
       </c>
     </row>
     <row r="40">
@@ -4538,7 +4490,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="b">
@@ -4600,7 +4552,7 @@
       </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB40" t="n">
         <v>1.234112340940881</v>
@@ -4609,7 +4561,7 @@
         <v>4.358793022297943</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.3875549817250777</v>
+        <v>0.3527832595484278</v>
       </c>
     </row>
     <row r="41">
@@ -4640,7 +4592,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="b">
@@ -4702,7 +4654,7 @@
       </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB41" t="n">
         <v>1.234112340940881</v>
@@ -4711,7 +4663,7 @@
         <v>4.301783294329191</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.01009350685791052</v>
+        <v>0.8096061693221636</v>
       </c>
     </row>
     <row r="42">
@@ -4742,7 +4694,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="b">
@@ -4804,7 +4756,7 @@
       </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB42" t="n">
         <v>1.234112340940881</v>
@@ -4813,7 +4765,7 @@
         <v>4.792946619091222</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.019702081484387</v>
+        <v>1.831541740089951</v>
       </c>
     </row>
     <row r="43">
@@ -4844,7 +4796,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="b">
@@ -4906,7 +4858,7 @@
       </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB43" t="n">
         <v>1.234112340940881</v>
@@ -4915,7 +4867,7 @@
         <v>4.836014233998348</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.9678326950121794</v>
+        <v>1.721605547420103</v>
       </c>
     </row>
     <row r="44">
@@ -4946,7 +4898,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="b">
@@ -5008,7 +4960,7 @@
       </c>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB44" t="n">
         <v>1.234112340940881</v>
@@ -5017,7 +4969,7 @@
         <v>4.96006747439421</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.094455554827597</v>
+        <v>1.836605751353115</v>
       </c>
     </row>
     <row r="45">
@@ -5048,7 +5000,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="b">
@@ -5110,7 +5062,7 @@
       </c>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB45" t="n">
         <v>1.214405758904478</v>
@@ -5119,7 +5071,7 @@
         <v>4.993319588112083</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.2940565855905599</v>
+        <v>0.7902658217974037</v>
       </c>
     </row>
     <row r="46">
@@ -5150,7 +5102,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="b">
@@ -5212,7 +5164,7 @@
       </c>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB46" t="n">
         <v>1.214405758904478</v>
@@ -5221,7 +5173,7 @@
         <v>4.981467438485524</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.3600948023086388</v>
+        <v>0.05453956195208267</v>
       </c>
     </row>
     <row r="47">
@@ -5252,7 +5204,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="b">
@@ -5314,7 +5266,7 @@
       </c>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB47" t="n">
         <v>1.214405758904478</v>
@@ -5323,7 +5275,7 @@
         <v>4.977993259349364</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.2282235247854183</v>
+        <v>0.2596548867043438</v>
       </c>
     </row>
     <row r="48">
@@ -5354,7 +5306,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="b">
@@ -5416,7 +5368,7 @@
       </c>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB48" t="n">
         <v>1.214405758904478</v>
@@ -5425,7 +5377,7 @@
         <v>4.979845780847799</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.002253532029505006</v>
+        <v>0.4860215818644205</v>
       </c>
     </row>
     <row r="49">
@@ -5456,7 +5408,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="b">
@@ -5518,7 +5470,7 @@
       </c>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB49" t="n">
         <v>1.214405758904478</v>
@@ -5527,7 +5479,7 @@
         <v>4.99835473558256</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.9878825707465823</v>
+        <v>1.428851073891493</v>
       </c>
     </row>
     <row r="50">
@@ -5558,7 +5510,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="b">
@@ -5620,7 +5572,7 @@
       </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB50" t="n">
         <v>1.214405758904478</v>
@@ -5629,7 +5581,7 @@
         <v>4.995683419334862</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.458968868307478</v>
+        <v>0.1741032869194121</v>
       </c>
     </row>
     <row r="51">
@@ -5660,7 +5612,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="b">
@@ -5722,7 +5674,7 @@
       </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB51" t="n">
         <v>1.198456990408521</v>
@@ -5731,7 +5683,7 @@
         <v>4.919756464064288</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.02539249303125381</v>
+        <v>0.4587775845847126</v>
       </c>
     </row>
     <row r="52">
@@ -5762,7 +5714,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="b">
@@ -5824,7 +5776,7 @@
       </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB52" t="n">
         <v>1.198456990408521</v>
@@ -5833,7 +5785,7 @@
         <v>4.947424366230646</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.3796033943112999</v>
+        <v>0.06223426951769264</v>
       </c>
     </row>
     <row r="53">
@@ -5864,7 +5816,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="b">
@@ -5926,7 +5878,7 @@
       </c>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB53" t="n">
         <v>1.198456990408521</v>
@@ -5935,7 +5887,7 @@
         <v>4.850032454333542</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.180711491428283</v>
+        <v>0.6461429133778828</v>
       </c>
     </row>
     <row r="54">
@@ -5966,7 +5918,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="b">
@@ -6028,7 +5980,7 @@
       </c>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB54" t="n">
         <v>1.198456990408521</v>
@@ -6037,7 +5989,7 @@
         <v>4.595057252698465</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.598060235373236</v>
+        <v>2.38821816316985</v>
       </c>
     </row>
     <row r="55">
@@ -6068,7 +6020,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="b">
@@ -6130,7 +6082,7 @@
       </c>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB55" t="n">
         <v>1.198456990408521</v>
@@ -6139,7 +6091,7 @@
         <v>4.251828393683224</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.456059184094869</v>
+        <v>1.908556926222579</v>
       </c>
     </row>
     <row r="56">
@@ -6170,7 +6122,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="b">
@@ -6232,7 +6184,7 @@
       </c>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB56" t="n">
         <v>1.198456990408521</v>
@@ -6241,7 +6193,7 @@
         <v>4.365285891524879</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.6250893101926874</v>
+        <v>0.1811146290742471</v>
       </c>
     </row>
     <row r="57">
@@ -6272,7 +6224,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="b">
@@ -6334,7 +6286,7 @@
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB57" t="n">
         <v>1.187028539380273</v>
@@ -6343,7 +6295,7 @@
         <v>4.481831062623345</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.02408990556863724</v>
+        <v>0.6208024919254477</v>
       </c>
     </row>
     <row r="58">
@@ -6374,7 +6326,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="b">
@@ -6436,7 +6388,7 @@
       </c>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB58" t="n">
         <v>1.187028539380273</v>
@@ -6445,7 +6397,7 @@
         <v>4.611224079101234</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.794058059592722</v>
+        <v>1.429331005900099</v>
       </c>
     </row>
     <row r="59">
@@ -6476,7 +6428,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="b">
@@ -6538,7 +6490,7 @@
       </c>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB59" t="n">
         <v>1.187028539380273</v>
@@ -6547,7 +6499,7 @@
         <v>4.827639686867086</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.8082033387570765</v>
+        <v>1.310071626113771</v>
       </c>
     </row>
     <row r="60">
@@ -6578,7 +6530,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="b">
@@ -6640,7 +6592,7 @@
       </c>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB60" t="n">
         <v>1.187028539380273</v>
@@ -6649,7 +6601,7 @@
         <v>4.88379753772581</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.03470721144485275</v>
+        <v>0.4187504184285794</v>
       </c>
     </row>
     <row r="61">
@@ -6680,7 +6632,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="b">
@@ -6742,7 +6694,7 @@
       </c>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB61" t="n">
         <v>1.187028539380273</v>
@@ -6751,7 +6703,7 @@
         <v>4.832301918554789</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.9942341342545623</v>
+        <v>0.6430790768309413</v>
       </c>
     </row>
     <row r="62">
@@ -6782,7 +6734,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="b">
@@ -6844,7 +6796,7 @@
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB62" t="n">
         <v>1.187028539380273</v>
@@ -6853,7 +6805,7 @@
         <v>4.601737649248786</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.641145614497474</v>
+        <v>1.272369470201093</v>
       </c>
     </row>
     <row r="63">
@@ -6884,7 +6836,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="b">
@@ -6946,7 +6898,7 @@
       </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB63" t="n">
         <v>1.178988494574768</v>
@@ -6955,7 +6907,7 @@
         <v>4.498420423978368</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.9750442847647034</v>
+        <v>0.4755875672065445</v>
       </c>
     </row>
     <row r="64">
@@ -6986,7 +6938,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="b">
@@ -7048,7 +7000,7 @@
       </c>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB64" t="n">
         <v>1.178988494574768</v>
@@ -7057,7 +7009,7 @@
         <v>4.775585907092906</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.2451204177447777</v>
+        <v>0.4757528895412449</v>
       </c>
     </row>
     <row r="65">
@@ -7088,7 +7040,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="b">
@@ -7150,7 +7102,7 @@
       </c>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB65" t="n">
         <v>1.178988494574768</v>
@@ -7159,7 +7111,7 @@
         <v>4.817898935446795</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.184379839320776</v>
+        <v>0.965120265207051</v>
       </c>
     </row>
     <row r="66">
@@ -7190,7 +7142,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="b">
@@ -7252,7 +7204,7 @@
       </c>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB66" t="n">
         <v>1.178988494574768</v>
@@ -7261,7 +7213,7 @@
         <v>4.784306898377416</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.2029610412857683</v>
+        <v>0.8977295504537265</v>
       </c>
     </row>
     <row r="67">
@@ -7292,7 +7244,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="b">
@@ -7354,7 +7306,7 @@
       </c>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB67" t="n">
         <v>1.178988494574768</v>
@@ -7363,7 +7315,7 @@
         <v>4.761601088117617</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.2249169935303247</v>
+        <v>0.8889495491691366</v>
       </c>
     </row>
     <row r="68">
@@ -7394,7 +7346,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="b">
@@ -7456,7 +7408,7 @@
       </c>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB68" t="n">
         <v>1.178988494574768</v>
@@ -7465,7 +7417,7 @@
         <v>4.880240637477733</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.119277356749117</v>
+        <v>1.996340344505436</v>
       </c>
     </row>
     <row r="69">
@@ -7496,7 +7448,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="b">
@@ -7558,7 +7510,7 @@
       </c>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB69" t="n">
         <v>1.14678435220084</v>
@@ -7567,7 +7519,7 @@
         <v>4.911646694451397</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.421411597126311</v>
+        <v>2.181490975719008</v>
       </c>
     </row>
     <row r="70">
@@ -7598,7 +7550,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="b">
@@ -7660,7 +7612,7 @@
       </c>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB70" t="n">
         <v>1.14678435220084</v>
@@ -7669,7 +7621,7 @@
         <v>4.815237391153738</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.5612512248355571</v>
+        <v>1.122495409071314</v>
       </c>
     </row>
     <row r="71">
@@ -7700,7 +7652,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="b">
@@ -7762,7 +7714,7 @@
       </c>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB71" t="n">
         <v>1.14678435220084</v>
@@ -7771,7 +7723,7 @@
         <v>4.848641573580318</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.4870245658255875</v>
+        <v>1.036358380936172</v>
       </c>
     </row>
     <row r="72">
@@ -7802,7 +7754,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="b">
@@ -7864,7 +7816,7 @@
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB72" t="n">
         <v>1.14678435220084</v>
@@ -7873,7 +7825,7 @@
         <v>4.918068501822405</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.6241782567765269</v>
+        <v>1.10779379652071</v>
       </c>
     </row>
     <row r="73">
@@ -7904,7 +7856,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="b">
@@ -7966,7 +7918,7 @@
       </c>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB73" t="n">
         <v>1.14678435220084</v>
@@ -7975,7 +7927,7 @@
         <v>4.991274522897591</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.3545823201396694</v>
+        <v>0.002524465956003654</v>
       </c>
     </row>
     <row r="74">
@@ -8006,7 +7958,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="b">
@@ -8068,7 +8020,7 @@
       </c>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB74" t="n">
         <v>1.14678435220084</v>
@@ -8077,7 +8029,7 @@
         <v>4.979243107811824</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.613244379932913</v>
+        <v>1.335880312470967</v>
       </c>
     </row>
     <row r="75">
@@ -8108,10 +8060,10 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5272422850672178</v>
+        <v>0.5272591485083084</v>
       </c>
       <c r="I75" t="b">
         <v>1</v>
@@ -8147,21 +8099,21 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>soft_fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>soft_quality_gate</t>
+          <t>all_recovery_gates</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>contextual</t>
         </is>
       </c>
       <c r="V75" t="n">
-        <v>1.126484133557546</v>
+        <v>1.126656946794453</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
@@ -8174,7 +8126,7 @@
       </c>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB75" t="n">
         <v>1.135047426877491</v>
@@ -8183,7 +8135,7 @@
         <v>4.733086261734453</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.536161201213126</v>
+        <v>2.297804554963859</v>
       </c>
     </row>
     <row r="76">
@@ -8214,10 +8166,10 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5231134963623322</v>
+        <v>0.5231276378068725</v>
       </c>
       <c r="I76" t="b">
         <v>1</v>
@@ -8267,7 +8219,7 @@
         </is>
       </c>
       <c r="V76" t="n">
-        <v>0.8433817308731502</v>
+        <v>0.8432834892244356</v>
       </c>
       <c r="W76" t="n">
         <v>0.9722222222222222</v>
@@ -8280,7 +8232,7 @@
       </c>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB76" t="n">
         <v>1.135047426877491</v>
@@ -8289,7 +8241,7 @@
         <v>4.482461168906791</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.91198603056368</v>
+        <v>1.531766692193767</v>
       </c>
     </row>
     <row r="77">
@@ -8320,10 +8272,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5154956847950363</v>
+        <v>0.5155087495483448</v>
       </c>
       <c r="I77" t="b">
         <v>1</v>
@@ -8373,7 +8325,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>0.7087510981739439</v>
+        <v>0.7087178077431087</v>
       </c>
       <c r="W77" t="n">
         <v>0.9444444444444444</v>
@@ -8386,7 +8338,7 @@
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB77" t="n">
         <v>1.135047426877491</v>
@@ -8395,7 +8347,7 @@
         <v>4.338760552725467</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.76864701345355</v>
+        <v>1.321434752183059</v>
       </c>
     </row>
     <row r="78">
@@ -8426,10 +8378,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.5119057476102192</v>
+        <v>0.5119249983789139</v>
       </c>
       <c r="I78" t="b">
         <v>1</v>
@@ -8479,7 +8431,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>0.8607190209072511</v>
+        <v>0.8609625472867077</v>
       </c>
       <c r="W78" t="n">
         <v>0.7166666666666666</v>
@@ -8492,7 +8444,7 @@
       </c>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB78" t="n">
         <v>1.135047426877491</v>
@@ -8501,7 +8453,7 @@
         <v>4.494484808193954</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.582415001733704</v>
+        <v>1.198750439687991</v>
       </c>
     </row>
     <row r="79">
@@ -8532,10 +8484,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>0.4915316386970006</v>
+        <v>0.4915570539360681</v>
       </c>
       <c r="I79" t="b">
         <v>1</v>
@@ -8585,7 +8537,7 @@
         </is>
       </c>
       <c r="V79" t="n">
-        <v>0.2039898356940446</v>
+        <v>0.2042606042938338</v>
       </c>
       <c r="W79" t="n">
         <v>0.6888888888888889</v>
@@ -8598,7 +8550,7 @@
       </c>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB79" t="n">
         <v>1.135047426877491</v>
@@ -8607,7 +8559,7 @@
         <v>4.656815813987743</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.078512815830851</v>
+        <v>0.7110196687406632</v>
       </c>
     </row>
     <row r="80">
@@ -8638,10 +8590,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>0.4790928379712289</v>
+        <v>0.479116256187637</v>
       </c>
       <c r="I80" t="b">
         <v>1</v>
@@ -8691,7 +8643,7 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.4938758872675775</v>
+        <v>0.4938208027404641</v>
       </c>
       <c r="W80" t="n">
         <v>0.6611111111111112</v>
@@ -8704,7 +8656,7 @@
       </c>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB80" t="n">
         <v>1.135047426877491</v>
@@ -8713,7 +8665,7 @@
         <v>4.508619860008445</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.1379470355152901</v>
+        <v>0.1751638682862763</v>
       </c>
     </row>
     <row r="81">
@@ -8744,10 +8696,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4705769488963188</v>
+        <v>0.4706004877163197</v>
       </c>
       <c r="I81" t="b">
         <v>1</v>
@@ -8797,7 +8749,7 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>0.6444994205727866</v>
+        <v>0.6445218311280878</v>
       </c>
       <c r="W81" t="n">
         <v>0.6333333333333333</v>
@@ -8810,7 +8762,7 @@
       </c>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB81" t="n">
         <v>1.121581731628728</v>
@@ -8819,7 +8771,7 @@
         <v>4.804734596843327</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.0908441837129982</v>
+        <v>0.2732100238159283</v>
       </c>
     </row>
     <row r="82">
@@ -8850,10 +8802,10 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.4720401095570474</v>
+        <v>0.4720598839302167</v>
       </c>
       <c r="I82" t="b">
         <v>1</v>
@@ -8903,7 +8855,7 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>1.062185819520497</v>
+        <v>1.062022724242342</v>
       </c>
       <c r="W82" t="n">
         <v>0.6055555555555556</v>
@@ -8916,7 +8868,7 @@
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB82" t="n">
         <v>1.121581731628728</v>
@@ -8925,7 +8877,7 @@
         <v>4.753329265124515</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.3726827795471398</v>
+        <v>0.9189807336674344</v>
       </c>
     </row>
     <row r="83">
@@ -8956,10 +8908,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4759094658225498</v>
+        <v>0.4759236939528908</v>
       </c>
       <c r="I83" t="b">
         <v>1</v>
@@ -9009,7 +8961,7 @@
         </is>
       </c>
       <c r="V83" t="n">
-        <v>1.163941842532548</v>
+        <v>1.163699994606842</v>
       </c>
       <c r="W83" t="n">
         <v>0.5777777777777777</v>
@@ -9022,7 +8974,7 @@
       </c>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB83" t="n">
         <v>1.121581731628728</v>
@@ -9031,7 +8983,7 @@
         <v>4.904809366425277</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.6296486100509804</v>
+        <v>1.063639895502838</v>
       </c>
     </row>
     <row r="84">
@@ -9062,10 +9014,10 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.4688377151014522</v>
+        <v>0.4688475470376291</v>
       </c>
       <c r="I84" t="b">
         <v>1</v>
@@ -9115,7 +9067,7 @@
         </is>
       </c>
       <c r="V84" t="n">
-        <v>0.7028110920687429</v>
+        <v>0.702635233119444</v>
       </c>
       <c r="W84" t="n">
         <v>0.55</v>
@@ -9128,7 +9080,7 @@
       </c>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB84" t="n">
         <v>1.121581731628728</v>
@@ -9137,7 +9089,7 @@
         <v>4.931041095746235</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.09820703050806094</v>
+        <v>0.5137778843035151</v>
       </c>
     </row>
     <row r="85">
@@ -9168,10 +9120,10 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>0.4503965344427293</v>
+        <v>0.4504094810846235</v>
       </c>
       <c r="I85" t="b">
         <v>1</v>
@@ -9221,7 +9173,7 @@
         </is>
       </c>
       <c r="V85" t="n">
-        <v>0.2133234991671951</v>
+        <v>0.213472862575275</v>
       </c>
       <c r="W85" t="n">
         <v>0.5222222222222221</v>
@@ -9234,7 +9186,7 @@
       </c>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB85" t="n">
         <v>1.121581731628728</v>
@@ -9243,7 +9195,7 @@
         <v>4.816043471930991</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.34557588174972</v>
+        <v>0.8473742760253485</v>
       </c>
     </row>
     <row r="86">
@@ -9274,10 +9226,10 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.445711777318167</v>
+        <v>0.445723401143046</v>
       </c>
       <c r="I86" t="b">
         <v>1</v>
@@ -9327,7 +9279,7 @@
         </is>
       </c>
       <c r="V86" t="n">
-        <v>0.791971884048411</v>
+        <v>0.791919125223872</v>
       </c>
       <c r="W86" t="n">
         <v>0.4944444444444444</v>
@@ -9340,7 +9292,7 @@
       </c>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB86" t="n">
         <v>1.121581731628728</v>
@@ -9349,7 +9301,7 @@
         <v>4.816243448865423</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.605910398218652</v>
+        <v>1.376658987715208</v>
       </c>
     </row>
     <row r="87">
@@ -9380,10 +9332,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>0.4363320859342139</v>
+        <v>0.4363308864440011</v>
       </c>
       <c r="I87" t="b">
         <v>0</v>
@@ -9433,7 +9385,7 @@
         </is>
       </c>
       <c r="V87" t="n">
-        <v>0.5791140435915593</v>
+        <v>0.5785496262947845</v>
       </c>
       <c r="W87" t="n">
         <v>0.6666666666666667</v>
@@ -9446,7 +9398,7 @@
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB87" t="n">
         <v>1.234616607421834</v>
@@ -9455,7 +9407,7 @@
         <v>4.269517944259702</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.594008137664407</v>
+        <v>1.212850818192728</v>
       </c>
     </row>
     <row r="88">
@@ -9486,10 +9438,10 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>0.4232027737954991</v>
+        <v>0.4231787850703564</v>
       </c>
       <c r="I88" t="b">
         <v>0</v>
@@ -9539,7 +9491,7 @@
         </is>
       </c>
       <c r="V88" t="n">
-        <v>0.3981963480588858</v>
+        <v>0.3971501086786979</v>
       </c>
       <c r="W88" t="n">
         <v>0.6388888888888888</v>
@@ -9552,7 +9504,7 @@
       </c>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB88" t="n">
         <v>1.234616607421834</v>
@@ -9561,7 +9513,7 @@
         <v>4.244752468585613</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.11553849427156</v>
+        <v>0.6240411993118082</v>
       </c>
     </row>
     <row r="89">
@@ -9592,10 +9544,10 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.4093444696903859</v>
+        <v>0.4093416804369579</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
@@ -9645,7 +9597,7 @@
         </is>
       </c>
       <c r="V89" t="n">
-        <v>0.3450749870647164</v>
+        <v>0.3460397769657581</v>
       </c>
       <c r="W89" t="n">
         <v>0.6111111111111112</v>
@@ -9658,7 +9610,7 @@
       </c>
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB89" t="n">
         <v>1.234616607421834</v>
@@ -9667,7 +9619,7 @@
         <v>4.408817232874113</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.5234082560624255</v>
+        <v>0.1556937754235874</v>
       </c>
     </row>
     <row r="90">
@@ -9698,10 +9650,10 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4035343416558006</v>
+        <v>0.4035384025051538</v>
       </c>
       <c r="I90" t="b">
         <v>0</v>
@@ -9751,7 +9703,7 @@
         </is>
       </c>
       <c r="V90" t="n">
-        <v>0.7161252458605397</v>
+        <v>0.7164580002891837</v>
       </c>
       <c r="W90" t="n">
         <v>0.5833333333333333</v>
@@ -9764,7 +9716,7 @@
       </c>
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB90" t="n">
         <v>1.234616607421834</v>
@@ -9773,7 +9725,7 @@
         <v>4.750752805494402</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.3199048501461712</v>
+        <v>0.3089995068007292</v>
       </c>
     </row>
     <row r="91">
@@ -9804,10 +9756,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4043094905168191</v>
+        <v>0.4043103218805126</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -9857,7 +9809,7 @@
         </is>
       </c>
       <c r="V91" t="n">
-        <v>1.038417987318647</v>
+        <v>1.038257542309074</v>
       </c>
       <c r="W91" t="n">
         <v>0.5555555555555556</v>
@@ -9870,7 +9822,7 @@
       </c>
       <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB91" t="n">
         <v>1.234616607421834</v>
@@ -9879,7 +9831,7 @@
         <v>4.856754974715681</v>
       </c>
       <c r="AD91" t="n">
-        <v>0.1497400146187802</v>
+        <v>0.7313129410550523</v>
       </c>
     </row>
     <row r="92">
@@ -9910,10 +9862,10 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>0.394077651833156</v>
+        <v>0.3940735918467431</v>
       </c>
       <c r="I92" t="b">
         <v>0</v>
@@ -9963,7 +9915,7 @@
         </is>
       </c>
       <c r="V92" t="n">
-        <v>0.4938610681345134</v>
+        <v>0.4936201486938653</v>
       </c>
       <c r="W92" t="n">
         <v>0.5277777777777778</v>
@@ -9976,7 +9928,7 @@
       </c>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB92" t="n">
         <v>1.234616607421834</v>
@@ -9985,7 +9937,7 @@
         <v>4.979406780743572</v>
       </c>
       <c r="AD92" t="n">
-        <v>0.3984590072918108</v>
+        <v>0.1157277893484889</v>
       </c>
     </row>
     <row r="93">
@@ -10016,10 +9968,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3790615088948274</v>
+        <v>0.3790626507930778</v>
       </c>
       <c r="I93" t="b">
         <v>0</v>
@@ -10069,7 +10021,7 @@
         </is>
       </c>
       <c r="V93" t="n">
-        <v>0.2379094389911737</v>
+        <v>0.2381655932172634</v>
       </c>
       <c r="W93" t="n">
         <v>0.5</v>
@@ -10082,7 +10034,7 @@
       </c>
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB93" t="n">
         <v>1.424364730776262</v>
@@ -10091,7 +10043,7 @@
         <v>4.98943927881002</v>
       </c>
       <c r="AD93" t="n">
-        <v>0.9493073843860242</v>
+        <v>0.6193059223015625</v>
       </c>
     </row>
     <row r="94">
@@ -10122,10 +10074,10 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3746455887815606</v>
+        <v>0.3746518277316033</v>
       </c>
       <c r="I94" t="b">
         <v>0</v>
@@ -10175,7 +10127,7 @@
         </is>
       </c>
       <c r="V94" t="n">
-        <v>0.76700772778847</v>
+        <v>0.7672773589143589</v>
       </c>
       <c r="W94" t="n">
         <v>0.4722222222222222</v>
@@ -10188,7 +10140,7 @@
       </c>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB94" t="n">
         <v>1.424364730776262</v>
@@ -10197,7 +10149,7 @@
         <v>4.983473054396536</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.8903061033407509</v>
+        <v>0.603187827255117</v>
       </c>
     </row>
     <row r="95">
@@ -10228,10 +10180,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0.3620245308206345</v>
+        <v>0.3620327095356898</v>
       </c>
       <c r="I95" t="b">
         <v>0</v>
@@ -10281,7 +10233,7 @@
         </is>
       </c>
       <c r="V95" t="n">
-        <v>0.3262401406100753</v>
+        <v>0.3263549107811265</v>
       </c>
       <c r="W95" t="n">
         <v>0.4444444444444444</v>
@@ -10294,7 +10246,7 @@
       </c>
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB95" t="n">
         <v>1.424364730776262</v>
@@ -10303,7 +10255,7 @@
         <v>4.953610057049695</v>
       </c>
       <c r="AD95" t="n">
-        <v>0.1959120157641357</v>
+        <v>0.2565989598205699</v>
       </c>
     </row>
     <row r="96">
@@ -10334,10 +10286,10 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3620303274201049</v>
+        <v>0.3620378043885549</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
@@ -10387,7 +10339,7 @@
         </is>
       </c>
       <c r="V96" t="n">
-        <v>1.000320232413934</v>
+        <v>1.000281458151755</v>
       </c>
       <c r="W96" t="n">
         <v>0.4166666666666666</v>
@@ -10400,7 +10352,7 @@
       </c>
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB96" t="n">
         <v>1.424364730776262</v>
@@ -10409,7 +10361,7 @@
         <v>4.950493563874158</v>
       </c>
       <c r="AD96" t="n">
-        <v>0.9247653880096425</v>
+        <v>0.6320586150135928</v>
       </c>
     </row>
     <row r="97">
@@ -10440,10 +10392,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3440110277273197</v>
+        <v>0.3440211222378691</v>
       </c>
       <c r="I97" t="b">
         <v>0</v>
@@ -10493,7 +10445,7 @@
         </is>
       </c>
       <c r="V97" t="n">
-        <v>0.004541977397641212</v>
+        <v>0.004707136531549799</v>
       </c>
       <c r="W97" t="n">
         <v>0.3888888888888888</v>
@@ -10506,7 +10458,7 @@
       </c>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB97" t="n">
         <v>1.424364730776262</v>
@@ -10515,7 +10467,7 @@
         <v>4.999912789926316</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.2303107394210712</v>
+        <v>0.6711227830241955</v>
       </c>
     </row>
     <row r="98">
@@ -10546,10 +10498,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0.3417667805059497</v>
+        <v>0.3417836067323925</v>
       </c>
       <c r="I98" t="b">
         <v>0</v>
@@ -10599,7 +10551,7 @@
         </is>
       </c>
       <c r="V98" t="n">
-        <v>0.8695246930776334</v>
+        <v>0.8699198763772744</v>
       </c>
       <c r="W98" t="n">
         <v>0.3611111111111112</v>
@@ -10612,7 +10564,7 @@
       </c>
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB98" t="n">
         <v>1.424364730776262</v>
@@ -10621,7 +10573,7 @@
         <v>4.999051241231199</v>
       </c>
       <c r="AD98" t="n">
-        <v>0.754190910247347</v>
+        <v>0.4348531773768161</v>
       </c>
     </row>
     <row r="99">
@@ -10652,10 +10604,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>0.3292612502835319</v>
+        <v>0.3292815573715925</v>
       </c>
       <c r="I99" t="b">
         <v>0</v>
@@ -10705,7 +10657,7 @@
         </is>
       </c>
       <c r="V99" t="n">
-        <v>0.2681833966481703</v>
+        <v>0.2684231124877352</v>
       </c>
       <c r="W99" t="n">
         <v>0.3333333333333334</v>
@@ -10718,7 +10670,7 @@
       </c>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB99" t="n">
         <v>1.768764525300762</v>
@@ -10727,7 +10679,7 @@
         <v>4.793608863176694</v>
       </c>
       <c r="AD99" t="n">
-        <v>0.7531472490809129</v>
+        <v>0.2006431694159181</v>
       </c>
     </row>
     <row r="100">
@@ -10758,10 +10710,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>0.3165675902833128</v>
+        <v>0.3165853778616216</v>
       </c>
       <c r="I100" t="b">
         <v>0</v>
@@ -10811,7 +10763,7 @@
         </is>
       </c>
       <c r="V100" t="n">
-        <v>0.2289611978762493</v>
+        <v>0.2288557178048508</v>
       </c>
       <c r="W100" t="n">
         <v>0.3055555555555556</v>
@@ -10824,7 +10776,7 @@
       </c>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB100" t="n">
         <v>1.768764525300762</v>
@@ -10833,7 +10785,7 @@
         <v>4.499801426113609</v>
       </c>
       <c r="AD100" t="n">
-        <v>0.5868544932907882</v>
+        <v>0.07625927776122379</v>
       </c>
     </row>
     <row r="101">
@@ -10864,10 +10816,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>0.3090471020165558</v>
+        <v>0.3090637243045352</v>
       </c>
       <c r="I101" t="b">
         <v>0</v>
@@ -10917,7 +10869,7 @@
         </is>
       </c>
       <c r="V101" t="n">
-        <v>0.5248731394122551</v>
+        <v>0.5248262185770244</v>
       </c>
       <c r="W101" t="n">
         <v>0.2777777777777778</v>
@@ -10930,7 +10882,7 @@
       </c>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB101" t="n">
         <v>1.768764525300762</v>
@@ -10939,7 +10891,7 @@
         <v>4.736745486933463</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.337635925497269</v>
+        <v>0.7109325600113128</v>
       </c>
     </row>
     <row r="102">
@@ -10970,10 +10922,10 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>0.3095768159648286</v>
+        <v>0.3095982506589648</v>
       </c>
       <c r="I102" t="b">
         <v>0</v>
@@ -11023,7 +10975,7 @@
         </is>
       </c>
       <c r="V102" t="n">
-        <v>1.034280466946064</v>
+        <v>1.034590041625397</v>
       </c>
       <c r="W102" t="n">
         <v>0.25</v>
@@ -11036,7 +10988,7 @@
       </c>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB102" t="n">
         <v>1.768764525300762</v>
@@ -11045,7 +10997,7 @@
         <v>4.708488137306476</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.316767546631576</v>
+        <v>1.677729680185339</v>
       </c>
     </row>
     <row r="103">
@@ -11076,10 +11028,10 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>0.3125804257943795</v>
+        <v>0.3126066828583107</v>
       </c>
       <c r="I103" t="b">
         <v>0</v>
@@ -11129,7 +11081,7 @@
         </is>
       </c>
       <c r="V103" t="n">
-        <v>1.194046173657413</v>
+        <v>1.19434426344093</v>
       </c>
       <c r="W103" t="n">
         <v>0.2222222222222222</v>
@@ -11142,7 +11094,7 @@
       </c>
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB103" t="n">
         <v>1.768764525300762</v>
@@ -11151,7 +11103,7 @@
         <v>4.507430800085446</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.444168448157219</v>
+        <v>1.821955568786368</v>
       </c>
     </row>
     <row r="104">
@@ -11182,10 +11134,10 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2999873282594869</v>
+        <v>0.3000129176268975</v>
       </c>
       <c r="I104" t="b">
         <v>0</v>
@@ -11235,7 +11187,7 @@
         </is>
       </c>
       <c r="V104" t="n">
-        <v>0.1942491278595562</v>
+        <v>0.1942740880481269</v>
       </c>
       <c r="W104" t="n">
         <v>0.1944444444444444</v>
@@ -11248,7 +11200,7 @@
       </c>
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB104" t="n">
         <v>1.768764525300762</v>
@@ -11257,7 +11209,7 @@
         <v>4.558116511662621</v>
       </c>
       <c r="AD104" t="n">
-        <v>1.716460546537539</v>
+        <v>0.9596419123102409</v>
       </c>
     </row>
     <row r="105">
@@ -11288,10 +11240,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>0.3024988878079367</v>
+        <v>0.3025242169979033</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
@@ -11341,7 +11293,7 @@
         </is>
       </c>
       <c r="V105" t="n">
-        <v>1.167444375935595</v>
+        <v>1.167412749482263</v>
       </c>
       <c r="W105" t="n">
         <v>0.1666666666666666</v>
@@ -11354,7 +11306,7 @@
       </c>
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB105" t="n">
         <v>2.289997458454789</v>
@@ -11363,7 +11315,7 @@
         <v>4.807472971028428</v>
       </c>
       <c r="AD105" t="n">
-        <v>0.3873148488610987</v>
+        <v>0.4148767645834612</v>
       </c>
     </row>
     <row r="106">
@@ -11394,10 +11346,10 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>0.3112216554552494</v>
+        <v>0.3112435568875913</v>
       </c>
       <c r="I106" t="b">
         <v>0</v>
@@ -11447,7 +11399,7 @@
         </is>
       </c>
       <c r="V106" t="n">
-        <v>1.57671403095214</v>
+        <v>1.576439134441157</v>
       </c>
       <c r="W106" t="n">
         <v>0.1388888888888888</v>
@@ -11460,7 +11412,7 @@
       </c>
       <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB106" t="n">
         <v>2.289997458454789</v>
@@ -11469,7 +11421,7 @@
         <v>4.790024169737451</v>
       </c>
       <c r="AD106" t="n">
-        <v>0.03919093558398535</v>
+        <v>0.8356063011502296</v>
       </c>
     </row>
     <row r="107">
@@ -11500,10 +11452,10 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>0.3234092830016733</v>
+        <v>0.3234263039038202</v>
       </c>
       <c r="I107" t="b">
         <v>0</v>
@@ -11553,7 +11505,7 @@
         </is>
       </c>
       <c r="V107" t="n">
-        <v>1.783212050497971</v>
+        <v>1.78284332296259</v>
       </c>
       <c r="W107" t="n">
         <v>0.1111111111111112</v>
@@ -11566,7 +11518,7 @@
       </c>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB107" t="n">
         <v>2.289997458454789</v>
@@ -11575,7 +11527,7 @@
         <v>4.870074753924777</v>
       </c>
       <c r="AD107" t="n">
-        <v>0.5378428038246474</v>
+        <v>1.281760700042139</v>
       </c>
     </row>
     <row r="108">
@@ -11606,10 +11558,10 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>0.3152385958392485</v>
+        <v>0.3152516907733997</v>
       </c>
       <c r="I108" t="b">
         <v>0</v>
@@ -11659,7 +11611,7 @@
         </is>
       </c>
       <c r="V108" t="n">
-        <v>0.4947153596464571</v>
+        <v>0.4944991776023612</v>
       </c>
       <c r="W108" t="n">
         <v>0.08333333333333337</v>
@@ -11672,7 +11624,7 @@
       </c>
       <c r="Z108" t="inlineStr"/>
       <c r="AA108" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB108" t="n">
         <v>2.289997458454789</v>
@@ -11681,7 +11633,7 @@
         <v>4.577124131558561</v>
       </c>
       <c r="AD108" t="n">
-        <v>0.810289931617606</v>
+        <v>0.1680300507882324</v>
       </c>
     </row>
     <row r="109">
@@ -11712,10 +11664,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3131107572506735</v>
+        <v>0.3131262093240502</v>
       </c>
       <c r="I109" t="b">
         <v>0</v>
@@ -11765,7 +11717,7 @@
         </is>
       </c>
       <c r="V109" t="n">
-        <v>0.8650013915389989</v>
+        <v>0.8651565392632747</v>
       </c>
       <c r="W109" t="n">
         <v>0.05555555555555558</v>
@@ -11778,7 +11730,7 @@
       </c>
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB109" t="n">
         <v>2.289997458454789</v>
@@ -11787,7 +11739,7 @@
         <v>4.498627990821739</v>
       </c>
       <c r="AD109" t="n">
-        <v>1.986524184384518</v>
+        <v>1.384762000952313</v>
       </c>
     </row>
     <row r="110">
@@ -11818,10 +11770,10 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>0.3189061927511327</v>
+        <v>0.318920371225582</v>
       </c>
       <c r="I110" t="b">
         <v>0</v>
@@ -11871,7 +11823,7 @@
         </is>
       </c>
       <c r="V110" t="n">
-        <v>1.370184375097629</v>
+        <v>1.370084760010334</v>
       </c>
       <c r="W110" t="n">
         <v>0.02777777777777779</v>
@@ -11884,7 +11836,7 @@
       </c>
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB110" t="n">
         <v>2.289997458454789</v>
@@ -11893,7 +11845,7 @@
         <v>4.603474990856743</v>
       </c>
       <c r="AD110" t="n">
-        <v>2.364406304973759</v>
+        <v>1.681858069885381</v>
       </c>
     </row>
     <row r="111">
@@ -11912,10 +11864,10 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>0.3170028684978147</v>
+        <v>0.3170066491626896</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -11965,7 +11917,7 @@
         </is>
       </c>
       <c r="V111" t="n">
-        <v>0.8806342243216715</v>
+        <v>0.8799874679978501</v>
       </c>
       <c r="W111" t="n">
         <v>0</v>
@@ -11982,7 +11934,7 @@
         </is>
       </c>
       <c r="AA111" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB111" t="n">
         <v>3.838671814628389</v>
@@ -11991,7 +11943,7 @@
         <v>4.618802588552084</v>
       </c>
       <c r="AD111" t="n">
-        <v>1.954044394072597</v>
+        <v>1.135983531235244</v>
       </c>
     </row>
     <row r="112">
@@ -12010,10 +11962,10 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>0.3113395173663238</v>
+        <v>0.3113249869511757</v>
       </c>
       <c r="I112" t="b">
         <v>0</v>
@@ -12063,7 +12015,7 @@
         </is>
       </c>
       <c r="V112" t="n">
-        <v>0.6426940135697945</v>
+        <v>0.6415430258941963</v>
       </c>
       <c r="W112" t="n">
         <v>0</v>
@@ -12076,7 +12028,7 @@
       </c>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB112" t="n">
         <v>3.838671814628389</v>
@@ -12085,7 +12037,7 @@
         <v>4.425395781287436</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.485921114653266</v>
+        <v>0.7843065332674538</v>
       </c>
     </row>
     <row r="113">
@@ -12104,10 +12056,10 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>0.2994546537554432</v>
+        <v>0.2994567644833374</v>
       </c>
       <c r="I113" t="b">
         <v>0</v>
@@ -12157,7 +12109,7 @@
         </is>
       </c>
       <c r="V113" t="n">
-        <v>0.2365335623683914</v>
+        <v>0.2375669820746187</v>
       </c>
       <c r="W113" t="n">
         <v>0</v>
@@ -12170,7 +12122,7 @@
       </c>
       <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="n">
-        <v>4.074099133996071</v>
+        <v>4.96734971538736</v>
       </c>
       <c r="AB113" t="n">
         <v>3.838671814628389</v>
@@ -12179,7 +12131,7 @@
         <v>4.708627699643031</v>
       </c>
       <c r="AD113" t="n">
-        <v>0.8851146983282296</v>
+        <v>0.02114357429677545</v>
       </c>
     </row>
     <row r="114">
@@ -12198,10 +12150,10 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>0.2951909120858286</v>
+        <v>0.2951983298719954</v>
       </c>
       <c r="I114" t="b">
         <v>0</v>
@@ -12251,7 +12203,7 @@
         </is>
       </c>
       <c r="V114" t="n">
-        <v>0.7152328997967963</v>
+        <v>0.7155893526940883</v>
       </c>
       <c r="W114" t="n">
         <v>0</v>
@@ -12264,7 +12216,7 @@
       </c>
       <c r="Z114" t="inlineStr"/>
       <c r="AA114" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB114" t="n">
         <v>3.838671814628389</v>
@@ -12273,7 +12225,7 @@
         <v>4.71908659515131</v>
       </c>
       <c r="AD114" t="n">
-        <v>0.6534532596910909</v>
+        <v>0.2452868583478565</v>
       </c>
     </row>
     <row r="115">
@@ -12292,10 +12244,10 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>0.2977745893346269</v>
+        <v>0.2977793227502358</v>
       </c>
       <c r="I115" t="b">
         <v>0</v>
@@ -12345,7 +12297,7 @@
         </is>
       </c>
       <c r="V115" t="n">
-        <v>1.17505127312639</v>
+        <v>1.174865005459857</v>
       </c>
       <c r="W115" t="n">
         <v>0</v>
@@ -12358,7 +12310,7 @@
       </c>
       <c r="Z115" t="inlineStr"/>
       <c r="AA115" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB115" t="n">
         <v>3.838671814628389</v>
@@ -12367,7 +12319,7 @@
         <v>4.78088934586181</v>
       </c>
       <c r="AD115" t="n">
-        <v>0.3238991870471258</v>
+        <v>0.4679036325385703</v>
       </c>
     </row>
     <row r="116">
@@ -12386,10 +12338,10 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2941607564907603</v>
+        <v>0.2941614742857056</v>
       </c>
       <c r="I116" t="b">
         <v>0</v>
@@ -12439,7 +12391,7 @@
         </is>
       </c>
       <c r="V116" t="n">
-        <v>0.757277284677543</v>
+        <v>0.7570114384627916</v>
       </c>
       <c r="W116" t="n">
         <v>0</v>
@@ -12452,7 +12404,7 @@
       </c>
       <c r="Z116" t="inlineStr"/>
       <c r="AA116" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB116" t="n">
         <v>3.838671814628389</v>
@@ -12461,7 +12413,7 @@
         <v>4.968336552009801</v>
       </c>
       <c r="AD116" t="n">
-        <v>0.3761852882130349</v>
+        <v>0.251141220696338</v>
       </c>
     </row>
     <row r="117">
@@ -12480,10 +12432,10 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>0.287496692780071</v>
+        <v>0.2874934684736454</v>
       </c>
       <c r="I117" t="b">
         <v>0</v>
@@ -12533,7 +12485,7 @@
         </is>
       </c>
       <c r="V117" t="n">
-        <v>0.5469100780002454</v>
+        <v>0.5466431606482992</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
@@ -12546,7 +12498,7 @@
       </c>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB117" t="n">
         <v>4.030596430542873</v>
@@ -12555,7 +12507,7 @@
         <v>4.980212932021827</v>
       </c>
       <c r="AD117" t="n">
-        <v>0.4253144371156277</v>
+        <v>0.08696147264102269</v>
       </c>
     </row>
     <row r="118">
@@ -12574,10 +12526,10 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0.2775164513114371</v>
+        <v>0.277517425314198</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
@@ -12627,7 +12579,7 @@
         </is>
       </c>
       <c r="V118" t="n">
-        <v>0.3057143459894691</v>
+        <v>0.3059986223400485</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
@@ -12640,7 +12592,7 @@
       </c>
       <c r="Z118" t="inlineStr"/>
       <c r="AA118" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB118" t="n">
         <v>4.030596430542873</v>
@@ -12649,7 +12601,7 @@
         <v>4.945018547851863</v>
       </c>
       <c r="AD118" t="n">
-        <v>0.6285709363488871</v>
+        <v>0.1203089641802569</v>
       </c>
     </row>
     <row r="119">
@@ -12668,10 +12620,10 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2640352983499498</v>
+        <v>0.2640344745896625</v>
       </c>
       <c r="I119" t="b">
         <v>0</v>
@@ -12721,7 +12673,7 @@
         </is>
       </c>
       <c r="V119" t="n">
-        <v>0.02844296993705948</v>
+        <v>0.02831681943788774</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -12734,7 +12686,7 @@
       </c>
       <c r="Z119" t="inlineStr"/>
       <c r="AA119" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB119" t="n">
         <v>4.030596430542873</v>
@@ -12743,7 +12695,7 @@
         <v>4.916926964055794</v>
       </c>
       <c r="AD119" t="n">
-        <v>0.03967277681433025</v>
+        <v>0.512962672906225</v>
       </c>
     </row>
     <row r="120">
@@ -12762,10 +12714,10 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2593770500723404</v>
+        <v>0.2593760023136871</v>
       </c>
       <c r="I120" t="b">
         <v>0</v>
@@ -12815,7 +12767,7 @@
         </is>
       </c>
       <c r="V120" t="n">
-        <v>0.6471495813839783</v>
+        <v>0.6471315131696224</v>
       </c>
       <c r="W120" t="n">
         <v>0</v>
@@ -12828,7 +12780,7 @@
       </c>
       <c r="Z120" t="inlineStr"/>
       <c r="AA120" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB120" t="n">
         <v>4.030596430542873</v>
@@ -12837,7 +12789,7 @@
         <v>4.999823011921628</v>
       </c>
       <c r="AD120" t="n">
-        <v>0.4501772304684233</v>
+        <v>0.1110144060670991</v>
       </c>
     </row>
     <row r="121">
@@ -12856,10 +12808,10 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2545423043722692</v>
+        <v>0.2545436408049475</v>
       </c>
       <c r="I121" t="b">
         <v>0</v>
@@ -12909,7 +12861,7 @@
         </is>
       </c>
       <c r="V121" t="n">
-        <v>0.6272032781063134</v>
+        <v>0.6273856127294771</v>
       </c>
       <c r="W121" t="n">
         <v>0</v>
@@ -12922,7 +12874,7 @@
       </c>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="n">
-        <v>4.600998043521259</v>
+        <v>4.995549855868559</v>
       </c>
       <c r="AB121" t="n">
         <v>4.030596430542873</v>
@@ -12931,7 +12883,7 @@
         <v>4.999919098698866</v>
       </c>
       <c r="AD121" t="n">
-        <v>0.2419511967831987</v>
+        <v>0.1657881114584565</v>
       </c>
     </row>
     <row r="122">
@@ -12950,10 +12902,10 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>0.2471203037671789</v>
+        <v>0.2471272780324205</v>
       </c>
       <c r="I122" t="b">
         <v>0</v>
@@ -13003,7 +12955,7 @@
         </is>
       </c>
       <c r="V122" t="n">
-        <v>0.4168355925437355</v>
+        <v>0.4172816300518024</v>
       </c>
       <c r="W122" t="n">
         <v>0</v>
@@ -13016,7 +12968,7 @@
       </c>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="n">
-        <v>4.600998043521259</v>
+        <v>4.995549855868559</v>
       </c>
       <c r="AB122" t="n">
         <v>4.030596430542873</v>
@@ -13025,7 +12977,7 @@
         <v>4.978600901600682</v>
       </c>
       <c r="AD122" t="n">
-        <v>0.4160951763844608</v>
+        <v>0.03793046000556195</v>
       </c>
     </row>
     <row r="123">
@@ -13044,10 +12996,10 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>0.2407170941408879</v>
+        <v>0.2407203029133147</v>
       </c>
       <c r="I123" t="b">
         <v>0</v>
@@ -13097,7 +13049,7 @@
         </is>
       </c>
       <c r="V123" t="n">
-        <v>0.4817738948456702</v>
+        <v>0.4814837787137934</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
@@ -13110,7 +13062,7 @@
       </c>
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="n">
-        <v>4.600998043521259</v>
+        <v>4.995549855868559</v>
       </c>
       <c r="AB123" t="n">
         <v>4.070694349944234</v>
@@ -13119,7 +13071,7 @@
         <v>4.773774871707418</v>
       </c>
       <c r="AD123" t="n">
-        <v>0.2585285007234125</v>
+        <v>0.6052524754800519</v>
       </c>
     </row>
     <row r="124">
@@ -13138,10 +13090,10 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>0.2374393502902892</v>
+        <v>0.2374435930177769</v>
       </c>
       <c r="I124" t="b">
         <v>0</v>
@@ -13191,7 +13143,7 @@
         </is>
       </c>
       <c r="V124" t="n">
-        <v>0.7276683766645795</v>
+        <v>0.7277579119100973</v>
       </c>
       <c r="W124" t="n">
         <v>0</v>
@@ -13204,7 +13156,7 @@
       </c>
       <c r="Z124" t="inlineStr"/>
       <c r="AA124" t="n">
-        <v>4.600998043521259</v>
+        <v>4.995549855868559</v>
       </c>
       <c r="AB124" t="n">
         <v>4.070694349944234</v>
@@ -13213,7 +13165,7 @@
         <v>4.624791361620153</v>
       </c>
       <c r="AD124" t="n">
-        <v>0.8556967859185366</v>
+        <v>1.483056392442373</v>
       </c>
     </row>
     <row r="125">
@@ -13232,10 +13184,10 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>0.2317859673997491</v>
+        <v>0.2317902316574361</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -13285,7 +13237,7 @@
         </is>
       </c>
       <c r="V125" t="n">
-        <v>0.5238040464962256</v>
+        <v>0.5238143688368532</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
@@ -13298,7 +13250,7 @@
       </c>
       <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="n">
-        <v>4.600998043521259</v>
+        <v>4.995549855868559</v>
       </c>
       <c r="AB125" t="n">
         <v>4.070694349944234</v>
@@ -13307,7 +13259,7 @@
         <v>4.644386599028057</v>
       </c>
       <c r="AD125" t="n">
-        <v>0.4302382836204852</v>
+        <v>0.8930613776942559</v>
       </c>
     </row>
     <row r="126">
@@ -13326,10 +13278,10 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2271068286663905</v>
+        <v>0.2271064231096552</v>
       </c>
       <c r="I126" t="b">
         <v>0</v>
@@ -13379,7 +13331,7 @@
         </is>
       </c>
       <c r="V126" t="n">
-        <v>0.5962534931815995</v>
+        <v>0.5958579863966742</v>
       </c>
       <c r="W126" t="n">
         <v>0</v>
@@ -13392,7 +13344,7 @@
       </c>
       <c r="Z126" t="inlineStr"/>
       <c r="AA126" t="n">
-        <v>4.464288446703705</v>
+        <v>4.991341432279834</v>
       </c>
       <c r="AB126" t="n">
         <v>4.070694349944234</v>
@@ -13401,7 +13353,7 @@
         <v>4.494029941504049</v>
       </c>
       <c r="AD126" t="n">
-        <v>0.6416451624933035</v>
+        <v>1.090996578683262</v>
       </c>
     </row>
     <row r="127">
@@ -13420,10 +13372,10 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>0.2184301195057294</v>
+        <v>0.2184250587877693</v>
       </c>
       <c r="I127" t="b">
         <v>0</v>
@@ -13473,7 +13425,7 @@
         </is>
       </c>
       <c r="V127" t="n">
-        <v>0.2358918301477633</v>
+        <v>0.2354805114697921</v>
       </c>
       <c r="W127" t="n">
         <v>0</v>
@@ -13486,7 +13438,7 @@
       </c>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="n">
-        <v>4.289973989151704</v>
+        <v>4.983169939854564</v>
       </c>
       <c r="AB127" t="n">
         <v>4.070694349944234</v>
@@ -13495,7 +13447,7 @@
         <v>4.685036395296541</v>
       </c>
       <c r="AD127" t="n">
-        <v>0.2709281291499896</v>
+        <v>0.2173374776435807</v>
       </c>
     </row>
     <row r="128">
@@ -13514,10 +13466,10 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2196947382937401</v>
+        <v>0.2196894017252664</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -13567,7 +13519,7 @@
         </is>
       </c>
       <c r="V128" t="n">
-        <v>1.115791612518664</v>
+        <v>1.11576903717129</v>
       </c>
       <c r="W128" t="n">
         <v>0</v>
@@ -13580,7 +13532,7 @@
       </c>
       <c r="Z128" t="inlineStr"/>
       <c r="AA128" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB128" t="n">
         <v>4.070694349944234</v>
@@ -13589,7 +13541,7 @@
         <v>4.675718686196508</v>
       </c>
       <c r="AD128" t="n">
-        <v>0.5717746389624343</v>
+        <v>0.7502355204005254</v>
       </c>
     </row>
     <row r="129">
@@ -13608,10 +13560,10 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2246548831353591</v>
+        <v>0.224650610949904</v>
       </c>
       <c r="I129" t="b">
         <v>0</v>
@@ -13661,7 +13613,7 @@
         </is>
       </c>
       <c r="V129" t="n">
-        <v>1.451548806324815</v>
+        <v>1.451656673983924</v>
       </c>
       <c r="W129" t="n">
         <v>0</v>
@@ -13674,7 +13626,7 @@
       </c>
       <c r="Z129" t="inlineStr"/>
       <c r="AA129" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB129" t="n">
         <v>4.178246035778852</v>
@@ -13683,7 +13635,7 @@
         <v>4.726180165535608</v>
       </c>
       <c r="AD129" t="n">
-        <v>0.3415632352891931</v>
+        <v>0.5440831846459047</v>
       </c>
     </row>
     <row r="130">
@@ -13702,10 +13654,10 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>0.2266701345601685</v>
+        <v>0.2266643587226301</v>
       </c>
       <c r="I130" t="b">
         <v>0</v>
@@ -13755,7 +13707,7 @@
         </is>
       </c>
       <c r="V130" t="n">
-        <v>1.179408646425476</v>
+        <v>1.179278192408315</v>
       </c>
       <c r="W130" t="n">
         <v>0</v>
@@ -13768,7 +13720,7 @@
       </c>
       <c r="Z130" t="inlineStr"/>
       <c r="AA130" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB130" t="n">
         <v>4.178246035778852</v>
@@ -13777,7 +13729,7 @@
         <v>4.696974503835822</v>
       </c>
       <c r="AD130" t="n">
-        <v>0.2518738181836994</v>
+        <v>0.5823234906003067</v>
       </c>
     </row>
     <row r="131">
@@ -13796,10 +13748,10 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2278687807582487</v>
+        <v>0.2278602799271738</v>
       </c>
       <c r="I131" t="b">
         <v>0</v>
@@ -13849,7 +13801,7 @@
         </is>
       </c>
       <c r="V131" t="n">
-        <v>1.105761281732689</v>
+        <v>1.105523533676248</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
@@ -13862,7 +13814,7 @@
       </c>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB131" t="n">
         <v>4.178246035778852</v>
@@ -13871,7 +13823,7 @@
         <v>4.770061349269651</v>
       </c>
       <c r="AD131" t="n">
-        <v>0.4673960663485591</v>
+        <v>0.656515437078565</v>
       </c>
     </row>
     <row r="132">
@@ -13890,10 +13842,10 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2210836370938434</v>
+        <v>0.2210731009444438</v>
       </c>
       <c r="I132" t="b">
         <v>0</v>
@@ -13943,7 +13895,7 @@
         </is>
       </c>
       <c r="V132" t="n">
-        <v>0.4044692176060931</v>
+        <v>0.4042683538439241</v>
       </c>
       <c r="W132" t="n">
         <v>0</v>
@@ -13956,7 +13908,7 @@
       </c>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB132" t="n">
         <v>4.178246035778852</v>
@@ -13965,7 +13917,7 @@
         <v>4.752320375193662</v>
       </c>
       <c r="AD132" t="n">
-        <v>0.2005335068873883</v>
+        <v>0.1813818236938732</v>
       </c>
     </row>
     <row r="133">
@@ -13984,10 +13936,10 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0.2255539873629351</v>
+        <v>0.2255463913270791</v>
       </c>
       <c r="I133" t="b">
         <v>0</v>
@@ -14037,7 +13989,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>1.404403539570337</v>
+        <v>1.404688798729924</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -14050,7 +14002,7 @@
       </c>
       <c r="Z133" t="inlineStr"/>
       <c r="AA133" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB133" t="n">
         <v>4.178246035778852</v>
@@ -14059,7 +14011,7 @@
         <v>4.613005093349326</v>
       </c>
       <c r="AD133" t="n">
-        <v>1.387374919820175</v>
+        <v>1.268202691552793</v>
       </c>
     </row>
     <row r="134">
@@ -14078,10 +14030,10 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2321301795280014</v>
+        <v>0.2321225995912972</v>
       </c>
       <c r="I134" t="b">
         <v>0</v>
@@ -14131,7 +14083,7 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>1.583114689476508</v>
+        <v>1.583135755400456</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -14144,7 +14096,7 @@
       </c>
       <c r="Z134" t="inlineStr"/>
       <c r="AA134" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB134" t="n">
         <v>4.178246035778852</v>
@@ -14153,7 +14105,7 @@
         <v>4.617316380660551</v>
       </c>
       <c r="AD134" t="n">
-        <v>1.275255391332855</v>
+        <v>1.270204808459978</v>
       </c>
     </row>
     <row r="135">
@@ -14172,10 +14124,10 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2241235974433002</v>
+        <v>0.224109113367462</v>
       </c>
       <c r="I135" t="b">
         <v>0</v>
@@ -14225,7 +14177,7 @@
         </is>
       </c>
       <c r="V135" t="n">
-        <v>0.3101644860671446</v>
+        <v>0.3095470895169405</v>
       </c>
       <c r="W135" t="n">
         <v>0</v>
@@ -14238,7 +14190,7 @@
       </c>
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="n">
-        <v>3.81620651046865</v>
+        <v>4.936894112978472</v>
       </c>
       <c r="AB135" t="n">
         <v>4.17889089263851</v>
@@ -14247,7 +14199,7 @@
         <v>4.761345941507582</v>
       </c>
       <c r="AD135" t="n">
-        <v>0.3705282885388259</v>
+        <v>0.227687507642384</v>
       </c>
     </row>
     <row r="136">
@@ -14266,10 +14218,10 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>0.2145441928139872</v>
+        <v>0.2145167876350671</v>
       </c>
       <c r="I136" t="b">
         <v>0</v>
@@ -14319,7 +14271,7 @@
         </is>
       </c>
       <c r="V136" t="n">
-        <v>0.1451676897399042</v>
+        <v>0.1439593340707426</v>
       </c>
       <c r="W136" t="n">
         <v>0</v>
@@ -14332,7 +14284,7 @@
       </c>
       <c r="Z136" t="inlineStr"/>
       <c r="AA136" t="n">
-        <v>3.521040891671006</v>
+        <v>4.878897232052198</v>
       </c>
       <c r="AB136" t="n">
         <v>4.17889089263851</v>
@@ -14341,7 +14293,7 @@
         <v>4.603326149986639</v>
       </c>
       <c r="AD136" t="n">
-        <v>0.4352701805552349</v>
+        <v>0.2429206159645785</v>
       </c>
     </row>
     <row r="137">
@@ -14360,10 +14312,10 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2164657437471068</v>
+        <v>0.2164517593541713</v>
       </c>
       <c r="I137" t="b">
         <v>0</v>
@@ -14413,7 +14365,7 @@
         </is>
       </c>
       <c r="V137" t="n">
-        <v>1.179128682805751</v>
+        <v>1.180402824453625</v>
       </c>
       <c r="W137" t="n">
         <v>0</v>
@@ -14426,7 +14378,7 @@
       </c>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB137" t="n">
         <v>4.17889089263851</v>
@@ -14435,7 +14387,7 @@
         <v>4.613270978162371</v>
       </c>
       <c r="AD137" t="n">
-        <v>0.4649287323440083</v>
+        <v>0.7334144107335746</v>
       </c>
     </row>
     <row r="138">
@@ -14454,10 +14406,10 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2200679413465531</v>
+        <v>0.2200588590373297</v>
       </c>
       <c r="I138" t="b">
         <v>0</v>
@@ -14507,7 +14459,7 @@
         </is>
       </c>
       <c r="V138" t="n">
-        <v>1.33281918303477</v>
+        <v>1.33329363493472</v>
       </c>
       <c r="W138" t="n">
         <v>0</v>
@@ -14520,7 +14472,7 @@
       </c>
       <c r="Z138" t="inlineStr"/>
       <c r="AA138" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB138" t="n">
         <v>4.17889089263851</v>
@@ -14529,7 +14481,7 @@
         <v>4.699515840646317</v>
       </c>
       <c r="AD138" t="n">
-        <v>0.2901915155808444</v>
+        <v>0.4778749665133054</v>
       </c>
     </row>
     <row r="139">
@@ -14548,10 +14500,10 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>0.2269675615419785</v>
+        <v>0.2269573220254617</v>
       </c>
       <c r="I139" t="b">
         <v>0</v>
@@ -14601,7 +14553,7 @@
         </is>
       </c>
       <c r="V139" t="n">
-        <v>1.627044552987414</v>
+        <v>1.626965259959096</v>
       </c>
       <c r="W139" t="n">
         <v>0</v>
@@ -14614,7 +14566,7 @@
       </c>
       <c r="Z139" t="inlineStr"/>
       <c r="AA139" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB139" t="n">
         <v>4.17889089263851</v>
@@ -14623,7 +14575,7 @@
         <v>4.774794641960089</v>
       </c>
       <c r="AD139" t="n">
-        <v>0.5319457445330892</v>
+        <v>0.7435738375468639</v>
       </c>
     </row>
     <row r="140">
@@ -14642,10 +14594,10 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>0.2293078795895583</v>
+        <v>0.2292954128926878</v>
       </c>
       <c r="I140" t="b">
         <v>0</v>
@@ -14695,7 +14647,7 @@
         </is>
       </c>
       <c r="V140" t="n">
-        <v>1.206224892374934</v>
+        <v>1.20603793227378</v>
       </c>
       <c r="W140" t="n">
         <v>0</v>
@@ -14708,7 +14660,7 @@
       </c>
       <c r="Z140" t="inlineStr"/>
       <c r="AA140" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB140" t="n">
         <v>4.17889089263851</v>
@@ -14717,7 +14669,7 @@
         <v>4.989485118503032</v>
       </c>
       <c r="AD140" t="n">
-        <v>0.2798649634860864</v>
+        <v>0.3981374948789668</v>
       </c>
     </row>
     <row r="141">
@@ -14736,10 +14688,10 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>0.2286284640447305</v>
+        <v>0.2286137741240358</v>
       </c>
       <c r="I141" t="b">
         <v>0</v>
@@ -14789,7 +14741,7 @@
         </is>
       </c>
       <c r="V141" t="n">
-        <v>0.940742067298877</v>
+        <v>0.9405449276064666</v>
       </c>
       <c r="W141" t="n">
         <v>0</v>
@@ -14802,7 +14754,7 @@
       </c>
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="n">
-        <v>3.199335989249912</v>
+        <v>4.770703296404525</v>
       </c>
       <c r="AB141" t="n">
         <v>4.256074816415946</v>
@@ -14811,7 +14763,7 @@
         <v>4.988161050824512</v>
       </c>
       <c r="AD141" t="n">
-        <v>0.5339866897121891</v>
+        <v>0.5463641045501929</v>
       </c>
     </row>
   </sheetData>
@@ -14950,7 +14902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-0.5477002137415199</v>
+        <v>-0.5503466269381078</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>45960</v>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV20_adapted_recovery_case_plot_data.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
